--- a/New folder/For_printing_tag_Upgraded/DB_files/combined_dry_weight_DB.xlsx
+++ b/New folder/For_printing_tag_Upgraded/DB_files/combined_dry_weight_DB.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\For_printing_tag_Upgraded_back_up\DB_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ooffice KST\New folder\All_random\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,7 +15,7 @@
     <sheet name="combined dry weight (2)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'combined dry weight (2)'!$A$1:$L$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'combined dry weight (2)'!$A$1:$L$96</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="166">
   <si>
     <t>Sr</t>
   </si>
@@ -112,6 +112,9 @@
     <t>800 x10 TUBES</t>
   </si>
   <si>
+    <t>ROXX GOLD JR.</t>
+  </si>
+  <si>
     <t>ROXX GOLD-KIRAN</t>
   </si>
   <si>
@@ -523,7 +526,16 @@
     <t>500/3 SHT CONTINOUS POLYESTER FILAMENT</t>
   </si>
   <si>
-    <t>ROXX SILVER</t>
+    <t>ROXX 100</t>
+  </si>
+  <si>
+    <t>2/40 SPUN POLYESTER YARN</t>
+  </si>
+  <si>
+    <t>ROXX 100-200gm</t>
+  </si>
+  <si>
+    <t>ROXX 100-100gm</t>
   </si>
 </sst>
 </file>
@@ -610,11 +622,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -675,10 +688,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 3" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -959,7 +983,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P93"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="19"/>
@@ -1017,10 +1041,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -1060,7 +1084,7 @@
         <v>4.9504950495049505</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N2" s="5">
         <v>0</v>
@@ -1080,7 +1104,7 @@
         <v>20</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F3" s="7">
         <v>60</v>
@@ -1103,7 +1127,7 @@
         <v>5.208333333333333</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N3" s="5">
         <v>0</v>
@@ -1146,7 +1170,7 @@
         <v>8.3166999334664009</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N4" s="5">
         <v>0</v>
@@ -1166,7 +1190,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F5" s="7">
         <v>60</v>
@@ -1190,7 +1214,7 @@
         <v>13.227513227513228</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N5" s="5">
         <v>0</v>
@@ -1210,7 +1234,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F6" s="7">
         <v>60</v>
@@ -1234,7 +1258,7 @@
         <v>5.9523809523809526</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N6" s="5">
         <v>0</v>
@@ -1248,7 +1272,7 @@
         <v>1208</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>161</v>
+        <v>24</v>
       </c>
       <c r="D7" s="7">
         <v>20</v>
@@ -1277,7 +1301,7 @@
         <v>9.8812276437224558</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N7" s="5">
         <v>0</v>
@@ -1291,7 +1315,7 @@
         <v>1210</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" s="7">
         <v>20</v>
@@ -1320,7 +1344,7 @@
         <v>4.9504950495049505</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N8" s="5">
         <v>0</v>
@@ -1334,7 +1358,7 @@
         <v>1211</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="7">
         <v>20</v>
@@ -1363,7 +1387,7 @@
         <v>4.9504950495049505</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N9" s="5">
         <v>0</v>
@@ -1383,13 +1407,13 @@
         <v>25</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" s="7">
         <v>120</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>22</v>
@@ -1406,7 +1430,7 @@
         <v>2</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N10" s="5">
         <v>0</v>
@@ -1420,13 +1444,13 @@
         <v>1301</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="7">
         <v>90</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11" s="7">
         <v>30</v>
@@ -1449,7 +1473,7 @@
         <v>7.4074074074074074</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N11" s="5">
         <v>0</v>
@@ -1463,19 +1487,19 @@
         <v>1302</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" s="7">
         <v>30</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F12" s="7">
         <v>100</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>22</v>
@@ -1493,7 +1517,7 @@
         <v>12.345679012345679</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N12" s="5">
         <v>0</v>
@@ -1507,13 +1531,13 @@
         <v>1303</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="7">
         <v>30</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F13" s="7">
         <v>100</v>
@@ -1536,7 +1560,7 @@
         <v>6.6533599467731195</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N13" s="5">
         <v>0</v>
@@ -1550,19 +1574,19 @@
         <v>1304</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="7">
         <v>30</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F14" s="7">
         <v>100</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>22</v>
@@ -1579,7 +1603,7 @@
         <v>3.3333333333333335</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N14" s="5">
         <v>0</v>
@@ -1593,13 +1617,13 @@
         <v>1401</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="7">
         <v>125</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F15" s="7">
         <v>20</v>
@@ -1622,7 +1646,7 @@
         <v>5.4535737268632127</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N15" s="5">
         <v>0</v>
@@ -1636,13 +1660,13 @@
         <v>4201</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" s="7">
         <v>24</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F16" s="7">
         <v>120</v>
@@ -1665,7 +1689,7 @@
         <v>8.2479668761650249</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N16" s="5">
         <v>0</v>
@@ -1679,13 +1703,13 @@
         <v>4202</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" s="7">
         <v>30</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F17" s="7">
         <v>100</v>
@@ -1708,7 +1732,7 @@
         <v>6.6225165562913908</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N17" s="5">
         <v>0</v>
@@ -1722,13 +1746,13 @@
         <v>4203</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D18" s="7">
         <v>40</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F18" s="7">
         <v>75</v>
@@ -1751,7 +1775,7 @@
         <v>12.195121951219512</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N18" s="5">
         <v>0</v>
@@ -1765,13 +1789,13 @@
         <v>4204</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" s="7">
         <v>60</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F19" s="7">
         <v>50</v>
@@ -1794,7 +1818,7 @@
         <v>8.1967213114754092</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N19" s="5">
         <v>0</v>
@@ -1808,13 +1832,13 @@
         <v>4206</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D20" s="7">
         <v>80</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F20" s="7">
         <v>40</v>
@@ -1837,7 +1861,7 @@
         <v>4.4444444444444446</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N20" s="5">
         <v>0</v>
@@ -1851,13 +1875,13 @@
         <v>4207</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21" s="7">
         <v>105</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F21" s="7">
         <v>25</v>
@@ -1880,7 +1904,7 @@
         <v>10</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N21" s="5">
         <v>0</v>
@@ -1894,13 +1918,13 @@
         <v>4208</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D22" s="7">
         <v>40</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F22" s="7">
         <v>75</v>
@@ -1923,7 +1947,7 @@
         <v>4.8780487804878048</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N22" s="5">
         <v>0</v>
@@ -1937,13 +1961,13 @@
         <v>4209</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D23" s="2">
         <v>24</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F23" s="2">
         <v>120</v>
@@ -1966,7 +1990,7 @@
         <v>8.2479668761650249</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N23" s="5">
         <v>0</v>
@@ -1980,13 +2004,13 @@
         <v>4210</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D24" s="7">
         <v>30</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F24" s="7">
         <v>100</v>
@@ -2009,7 +2033,7 @@
         <v>6.6225165562913908</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N24" s="5">
         <v>0</v>
@@ -2023,13 +2047,13 @@
         <v>4211</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D25" s="7">
         <v>40</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F25" s="7">
         <v>75</v>
@@ -2052,7 +2076,7 @@
         <v>12.195121951219512</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N25" s="5">
         <v>0</v>
@@ -2066,19 +2090,19 @@
         <v>4212</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D26" s="7">
         <v>30</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F26" s="7">
         <v>100</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>22</v>
@@ -2095,7 +2119,7 @@
         <v>3.3112582781456954</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N26" s="5">
         <v>0</v>
@@ -2109,19 +2133,19 @@
         <v>4213</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D27" s="7">
         <v>40</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F27" s="7">
         <v>75</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>22</v>
@@ -2138,7 +2162,7 @@
         <v>4.8780487804878048</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N27" s="5">
         <v>0</v>
@@ -2152,13 +2176,13 @@
         <v>4305</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D28" s="7">
         <v>90</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="7">
         <v>30</v>
@@ -2181,7 +2205,7 @@
         <v>3.0487804878048781</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N28" s="5">
         <v>0</v>
@@ -2195,13 +2219,13 @@
         <v>7102</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D29" s="7">
         <v>17</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F29" s="7">
         <v>160</v>
@@ -2224,7 +2248,7 @@
         <v>11.088933244621867</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N29" s="5">
         <v>0</v>
@@ -2238,13 +2262,13 @@
         <v>7103</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D30" s="7">
         <v>35</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F30" s="7">
         <v>80</v>
@@ -2267,7 +2291,7 @@
         <v>5.5444666223109333</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N30" s="5">
         <v>0</v>
@@ -2281,13 +2305,13 @@
         <v>7201</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D31" s="7">
         <v>18</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F31" s="7">
         <v>150</v>
@@ -2310,7 +2334,7 @@
         <v>5.5444666223109333</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N31" s="5">
         <v>0</v>
@@ -2324,13 +2348,13 @@
         <v>7301</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D32" s="7">
         <v>27</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F32" s="7">
         <v>120</v>
@@ -2353,7 +2377,7 @@
         <v>7.3529411764705879</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N32" s="5">
         <v>0</v>
@@ -2367,13 +2391,13 @@
         <v>2201</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D33" s="7">
         <v>50</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F33" s="7">
         <v>60</v>
@@ -2382,7 +2406,7 @@
         <v>10000</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>15</v>
@@ -2396,7 +2420,7 @@
         <v>2.0161696808403393</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N33" s="5">
         <v>0</v>
@@ -2410,13 +2434,13 @@
         <v>2202</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D34" s="7">
         <v>50</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F34" s="7">
         <v>60</v>
@@ -2425,7 +2449,7 @@
         <v>2000</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>15</v>
@@ -2439,7 +2463,7 @@
         <v>10.080848404201697</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N34" s="5">
         <v>0</v>
@@ -2453,13 +2477,13 @@
         <v>2203</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D35" s="7">
         <v>50</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F35" s="7">
         <v>60</v>
@@ -2468,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J35" s="9">
         <v>887</v>
@@ -2482,7 +2506,7 @@
         <v>1.1273957158962795</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N35" s="5">
         <v>0</v>
@@ -2496,13 +2520,13 @@
         <v>2204</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D36" s="11">
         <v>35</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F36" s="11">
         <v>80</v>
@@ -2511,7 +2535,7 @@
         <v>950</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I36" s="12" t="s">
         <v>17</v>
@@ -2520,14 +2544,14 @@
         <v>841</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L36" s="9">
         <f t="shared" si="0"/>
         <v>1.1890606420927468</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N36" s="5">
         <v>0</v>
@@ -2541,13 +2565,13 @@
         <v>2205</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D37" s="11">
         <v>50</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F37" s="11">
         <v>60</v>
@@ -2556,7 +2580,7 @@
         <v>950</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I37" s="12" t="s">
         <v>17</v>
@@ -2565,14 +2589,14 @@
         <v>841</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L37" s="9">
         <f t="shared" si="0"/>
         <v>1.1890606420927468</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N37" s="5">
         <v>0</v>
@@ -2586,13 +2610,13 @@
         <v>2206</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D38" s="11">
         <v>50</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F38" s="11">
         <v>60</v>
@@ -2601,7 +2625,7 @@
         <v>10000</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I38" s="12" t="s">
         <v>15</v>
@@ -2610,14 +2634,14 @@
         <v>495.99</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L38" s="9">
         <f t="shared" si="0"/>
         <v>2.0161696808403393</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N38" s="5">
         <v>0</v>
@@ -2631,13 +2655,13 @@
         <v>2207</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D39" s="7">
         <v>27</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F39" s="7">
         <v>120</v>
@@ -2646,7 +2670,7 @@
         <v>5000</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>15</v>
@@ -2660,7 +2684,7 @@
         <v>7.2582108510252219</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N39" s="5">
         <v>0</v>
@@ -2674,13 +2698,13 @@
         <v>2208</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D40" s="7">
         <v>30</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F40" s="7">
         <v>80</v>
@@ -2689,7 +2713,7 @@
         <v>5000</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>15</v>
@@ -2703,7 +2727,7 @@
         <v>5.7028799543769599</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N40" s="5">
         <v>0</v>
@@ -2717,13 +2741,13 @@
         <v>2209</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D41" s="7">
         <v>80</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F41" s="7">
         <v>30</v>
@@ -2732,7 +2756,7 @@
         <v>15000</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>15</v>
@@ -2746,7 +2770,7 @@
         <v>1.9047619047619047</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N41" s="5">
         <v>0</v>
@@ -2760,13 +2784,13 @@
         <v>2210</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D42" s="7">
         <v>35</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F42" s="7">
         <v>30</v>
@@ -2775,7 +2799,7 @@
         <v>15000</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>15</v>
@@ -2789,7 +2813,7 @@
         <v>1.9047619047619047</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N42" s="5">
         <v>0</v>
@@ -2803,13 +2827,13 @@
         <v>2211</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D43" s="7">
         <v>50</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F43" s="7">
         <v>60</v>
@@ -2818,10 +2842,10 @@
         <v>1</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J43" s="9">
         <v>930</v>
@@ -2832,7 +2856,7 @@
         <v>1.075268817204301</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N43" s="5">
         <v>0</v>
@@ -2846,13 +2870,13 @@
         <v>2301</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D44" s="7">
         <v>70</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F44" s="7">
         <v>40</v>
@@ -2861,7 +2885,7 @@
         <v>12000</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>15</v>
@@ -2875,7 +2899,7 @@
         <v>1.1273957158962795</v>
       </c>
       <c r="M44" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N44" s="5">
         <v>0</v>
@@ -2889,13 +2913,13 @@
         <v>2302</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D45" s="7">
         <v>70</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F45" s="7">
         <v>40</v>
@@ -2904,7 +2928,7 @@
         <v>7000</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>15</v>
@@ -2918,7 +2942,7 @@
         <v>1.9305019305019304</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N45" s="5">
         <v>0</v>
@@ -2932,13 +2956,13 @@
         <v>2303</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D46" s="7">
         <v>70</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F46" s="7">
         <v>40</v>
@@ -2947,7 +2971,7 @@
         <v>1500</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I46" s="8" t="s">
         <v>15</v>
@@ -2961,7 +2985,7 @@
         <v>8.9910269550988122</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N46" s="5">
         <v>0</v>
@@ -2975,13 +2999,13 @@
         <v>2304</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D47" s="7">
         <v>70</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F47" s="7">
         <v>40</v>
@@ -2990,7 +3014,7 @@
         <v>500</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>15</v>
@@ -3004,7 +3028,7 @@
         <v>26.973080865296435</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N47" s="5">
         <v>0</v>
@@ -3018,13 +3042,13 @@
         <v>2305</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D48" s="7">
         <v>70</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F48" s="7">
         <v>40</v>
@@ -3033,7 +3057,7 @@
         <v>10000</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I48" s="8" t="s">
         <v>15</v>
@@ -3047,7 +3071,7 @@
         <v>1.3513513513513513</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N48" s="5">
         <v>0</v>
@@ -3061,13 +3085,13 @@
         <v>2306</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D49" s="7">
         <v>90</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F49" s="7">
         <v>30</v>
@@ -3076,7 +3100,7 @@
         <v>1500</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>15</v>
@@ -3090,7 +3114,7 @@
         <v>7.6038399391692808</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N49" s="5">
         <v>0</v>
@@ -3104,13 +3128,13 @@
         <v>2307</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D50" s="7">
         <v>70</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F50" s="7">
         <v>40</v>
@@ -3119,10 +3143,10 @@
         <v>1</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J50" s="9">
         <v>887</v>
@@ -3133,7 +3157,7 @@
         <v>1.1273957158962795</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N50" s="5">
         <v>0</v>
@@ -3147,13 +3171,13 @@
         <v>2310</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D51" s="7">
         <v>135</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F51" s="7">
         <v>20</v>
@@ -3162,7 +3186,7 @@
         <v>5000</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>15</v>
@@ -3176,7 +3200,7 @@
         <v>1.3231713771567695</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N51" s="5">
         <v>0</v>
@@ -3190,13 +3214,13 @@
         <v>2311</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D52" s="7">
         <v>135</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F52" s="7">
         <v>20</v>
@@ -3205,7 +3229,7 @@
         <v>1000</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I52" s="8" t="s">
         <v>15</v>
@@ -3219,7 +3243,7 @@
         <v>6.5658157369471581</v>
       </c>
       <c r="M52" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N52" s="5">
         <v>0</v>
@@ -3233,13 +3257,13 @@
         <v>2313</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D53" s="11">
         <v>70</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F53" s="11">
         <v>40</v>
@@ -3248,7 +3272,7 @@
         <v>3000</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I53" s="12" t="s">
         <v>15</v>
@@ -3257,14 +3281,14 @@
         <v>222.44399999999999</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L53" s="9">
         <f t="shared" si="0"/>
         <v>4.4955134775494061</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N53" s="5">
         <v>0</v>
@@ -3278,13 +3302,13 @@
         <v>2314</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D54" s="11">
         <v>135</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F54" s="11">
         <v>20</v>
@@ -3293,7 +3317,7 @@
         <v>1500</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I54" s="12" t="s">
         <v>15</v>
@@ -3302,14 +3326,14 @@
         <v>228.45599999999999</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L54" s="9">
         <f t="shared" si="0"/>
         <v>4.377210491298106</v>
       </c>
       <c r="M54" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N54" s="5">
         <v>0</v>
@@ -3323,13 +3347,13 @@
         <v>2315</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D55" s="11">
         <v>70</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F55" s="11">
         <v>40</v>
@@ -3338,7 +3362,7 @@
         <v>3000</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I55" s="12" t="s">
         <v>15</v>
@@ -3347,14 +3371,14 @@
         <v>222.44399999999999</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L55" s="9">
         <f t="shared" si="0"/>
         <v>4.4955134775494061</v>
       </c>
       <c r="M55" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N55" s="5">
         <v>0</v>
@@ -3368,13 +3392,13 @@
         <v>2316</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D56" s="11">
         <v>135</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F56" s="11">
         <v>20</v>
@@ -3383,7 +3407,7 @@
         <v>1500</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I56" s="12" t="s">
         <v>15</v>
@@ -3392,14 +3416,14 @@
         <v>228.45599999999999</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L56" s="9">
         <f t="shared" si="0"/>
         <v>4.377210491298106</v>
       </c>
       <c r="M56" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N56" s="5">
         <v>0</v>
@@ -3413,13 +3437,13 @@
         <v>2317</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D57" s="11">
         <v>270</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F57" s="11">
         <v>10</v>
@@ -3428,7 +3452,7 @@
         <v>1000</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I57" s="12" t="s">
         <v>15</v>
@@ -3437,14 +3461,14 @@
         <v>316</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L57" s="9">
         <f t="shared" si="0"/>
         <v>3.1645569620253164</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N57" s="5">
         <v>0</v>
@@ -3458,13 +3482,13 @@
         <v>2318</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D58" s="11">
         <v>180</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F58" s="11">
         <v>15</v>
@@ -3473,7 +3497,7 @@
         <v>1500</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I58" s="12" t="s">
         <v>15</v>
@@ -3482,14 +3506,14 @@
         <v>262.5</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L58" s="9">
         <f t="shared" si="0"/>
         <v>3.8095238095238093</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N58" s="5">
         <v>0</v>
@@ -3503,13 +3527,13 @@
         <v>2319</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D59" s="11">
         <v>70</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F59" s="11">
         <v>40</v>
@@ -3518,7 +3542,7 @@
         <v>6500</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I59" s="12" t="s">
         <v>15</v>
@@ -3527,14 +3551,14 @@
         <v>481</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L59" s="9">
         <f t="shared" si="0"/>
         <v>2.0790020790020791</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N59" s="5">
         <v>0</v>
@@ -3548,13 +3572,13 @@
         <v>2320</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D60" s="7">
         <v>135</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F60" s="7">
         <v>20</v>
@@ -3563,7 +3587,7 @@
         <v>1000</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I60" s="8" t="s">
         <v>15</v>
@@ -3577,7 +3601,7 @@
         <v>6.5658157369471581</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N60" s="5">
         <v>0</v>
@@ -3591,13 +3615,13 @@
         <v>2321</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D61" s="11">
         <v>90</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F61" s="11">
         <v>30</v>
@@ -3606,7 +3630,7 @@
         <v>2500</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I61" s="12" t="s">
         <v>15</v>
@@ -3615,14 +3639,14 @@
         <v>219.1875</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L61" s="9">
         <f t="shared" si="0"/>
         <v>4.5623039635015683</v>
       </c>
       <c r="M61" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N61" s="5">
         <v>0</v>
@@ -3636,13 +3660,13 @@
         <v>2322</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D62" s="11">
         <v>45</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F62" s="11">
         <v>60</v>
@@ -3651,7 +3675,7 @@
         <v>5000</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I62" s="12" t="s">
         <v>15</v>
@@ -3660,14 +3684,14 @@
         <v>263.02499999999998</v>
       </c>
       <c r="K62" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L62" s="9">
         <f t="shared" si="0"/>
         <v>3.8019199695846404</v>
       </c>
       <c r="M62" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N62" s="5">
         <v>0</v>
@@ -3681,13 +3705,13 @@
         <v>2323</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D63" s="7">
         <v>135</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F63" s="7">
         <v>20</v>
@@ -3696,7 +3720,7 @@
         <v>1500</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I63" s="8" t="s">
         <v>15</v>
@@ -3710,7 +3734,7 @@
         <v>4.377210491298106</v>
       </c>
       <c r="M63" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N63" s="5">
         <v>0</v>
@@ -3724,13 +3748,13 @@
         <v>2324</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D64" s="7">
         <v>70</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F64" s="7">
         <v>40</v>
@@ -3739,7 +3763,7 @@
         <v>3000</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I64" s="8" t="s">
         <v>15</v>
@@ -3753,7 +3777,7 @@
         <v>4.4955134775494061</v>
       </c>
       <c r="M64" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N64" s="5">
         <v>0</v>
@@ -3767,13 +3791,13 @@
         <v>2325</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D65" s="7">
         <v>330</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F65" s="7">
         <v>8</v>
@@ -3782,7 +3806,7 @@
         <v>500</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>15</v>
@@ -3796,7 +3820,7 @@
         <v>5.617977528089888</v>
       </c>
       <c r="M65" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N65" s="5">
         <v>0</v>
@@ -3810,13 +3834,13 @@
         <v>2326</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D66" s="7">
         <v>70</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F66" s="7">
         <v>40</v>
@@ -3825,7 +3849,7 @@
         <v>1500</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I66" s="8" t="s">
         <v>15</v>
@@ -3839,7 +3863,7 @@
         <v>8.9910269550988122</v>
       </c>
       <c r="M66" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N66" s="5">
         <v>0</v>
@@ -3853,13 +3877,13 @@
         <v>3201</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D67" s="7">
         <v>50</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F67" s="7">
         <v>60</v>
@@ -3868,7 +3892,7 @@
         <v>1000</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I67" s="8" t="s">
         <v>15</v>
@@ -3882,7 +3906,7 @@
         <v>20.161696808403395</v>
       </c>
       <c r="M67" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N67" s="5">
         <v>0</v>
@@ -3896,13 +3920,13 @@
         <v>3202</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D68" s="7">
         <v>50</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F68" s="7">
         <v>60</v>
@@ -3911,7 +3935,7 @@
         <v>2000</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I68" s="8" t="s">
         <v>15</v>
@@ -3925,7 +3949,7 @@
         <v>10.080848404201697</v>
       </c>
       <c r="M68" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N68" s="5">
         <v>0</v>
@@ -3939,13 +3963,13 @@
         <v>3203</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D69" s="7">
         <v>50</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F69" s="7">
         <v>60</v>
@@ -3954,7 +3978,7 @@
         <v>500</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>15</v>
@@ -3968,7 +3992,7 @@
         <v>40.32339361680679</v>
       </c>
       <c r="M69" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N69" s="5">
         <v>0</v>
@@ -3982,13 +4006,13 @@
         <v>3301</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D70" s="7">
         <v>70</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F70" s="7">
         <v>40</v>
@@ -3997,7 +4021,7 @@
         <v>500</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I70" s="8" t="s">
         <v>15</v>
@@ -4011,7 +4035,7 @@
         <v>26.973080865296435</v>
       </c>
       <c r="M70" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N70" s="5">
         <v>0</v>
@@ -4025,13 +4049,13 @@
         <v>3302</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D71" s="7">
         <v>70</v>
       </c>
       <c r="E71" s="23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F71" s="7">
         <v>40</v>
@@ -4040,7 +4064,7 @@
         <v>1500</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I71" s="8" t="s">
         <v>15</v>
@@ -4054,7 +4078,7 @@
         <v>8.9910269550988122</v>
       </c>
       <c r="M71" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N71" s="5">
         <v>0</v>
@@ -4068,13 +4092,13 @@
         <v>3303</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D72" s="7">
         <v>70</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F72" s="7">
         <v>40</v>
@@ -4083,7 +4107,7 @@
         <v>1000</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I72" s="8" t="s">
         <v>15</v>
@@ -4097,7 +4121,7 @@
         <v>13.486540432648217</v>
       </c>
       <c r="M72" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N72" s="5">
         <v>0</v>
@@ -4111,13 +4135,13 @@
         <v>3304</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D73" s="7">
         <v>135</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F73" s="7">
         <v>20</v>
@@ -4126,7 +4150,7 @@
         <v>500</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I73" s="8" t="s">
         <v>15</v>
@@ -4140,7 +4164,7 @@
         <v>13.131631473894316</v>
       </c>
       <c r="M73" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N73" s="5">
         <v>0</v>
@@ -4154,13 +4178,13 @@
         <v>3310</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D74" s="7">
         <v>135</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F74" s="7">
         <v>20</v>
@@ -4169,7 +4193,7 @@
         <v>1000</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I74" s="8" t="s">
         <v>15</v>
@@ -4183,7 +4207,7 @@
         <v>6.5229019086010975</v>
       </c>
       <c r="M74" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N74" s="5">
         <v>0</v>
@@ -4197,13 +4221,13 @@
         <v>3311</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D75" s="7">
         <v>270</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F75" s="7">
         <v>10</v>
@@ -4212,7 +4236,7 @@
         <v>500</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I75" s="8" t="s">
         <v>15</v>
@@ -4226,7 +4250,7 @@
         <v>6.7226890756302522</v>
       </c>
       <c r="M75" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N75" s="5">
         <v>0</v>
@@ -4240,13 +4264,13 @@
         <v>3401</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D76" s="7">
         <v>90</v>
       </c>
       <c r="E76" s="21" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F76" s="7">
         <v>30</v>
@@ -4255,7 +4279,7 @@
         <v>1000</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I76" s="8" t="s">
         <v>15</v>
@@ -4269,7 +4293,7 @@
         <v>10.080848404201697</v>
       </c>
       <c r="M76" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N76" s="5">
         <v>0</v>
@@ -4283,13 +4307,13 @@
         <v>3402</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D77" s="7">
         <v>90</v>
       </c>
       <c r="E77" s="21" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F77" s="7">
         <v>30</v>
@@ -4298,7 +4322,7 @@
         <v>2000</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I77" s="8" t="s">
         <v>15</v>
@@ -4312,7 +4336,7 @@
         <v>5.7028799543769608</v>
       </c>
       <c r="M77" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N77" s="5">
         <v>0</v>
@@ -4326,13 +4350,13 @@
         <v>5301</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D78" s="7">
         <v>70</v>
       </c>
       <c r="E78" s="25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F78" s="7">
         <v>40</v>
@@ -4341,7 +4365,7 @@
         <v>1500</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I78" s="8" t="s">
         <v>15</v>
@@ -4355,10 +4379,10 @@
         <v>8.5299486497091284</v>
       </c>
       <c r="M78" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N78" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
@@ -4369,13 +4393,13 @@
         <v>5302</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D79" s="7">
         <v>135</v>
       </c>
       <c r="E79" s="25" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F79" s="7">
         <v>20</v>
@@ -4384,7 +4408,7 @@
         <v>1000</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I79" s="8" t="s">
         <v>15</v>
@@ -4398,7 +4422,7 @@
         <v>6.3365332826410672</v>
       </c>
       <c r="M79" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N79" s="5" t="e">
         <v>#N/A</v>
@@ -4412,13 +4436,13 @@
         <v>5304</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D80" s="11">
         <v>135</v>
       </c>
       <c r="E80" s="25" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F80" s="11">
         <v>20</v>
@@ -4427,7 +4451,7 @@
         <v>1500</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I80" s="12" t="s">
         <v>15</v>
@@ -4436,17 +4460,17 @@
         <v>236.7225</v>
       </c>
       <c r="K80" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L80" s="9">
         <f t="shared" si="1"/>
         <v>4.2243555217607112</v>
       </c>
       <c r="M80" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N80" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
@@ -4457,13 +4481,13 @@
         <v>5306</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D81" s="11">
         <v>135</v>
       </c>
       <c r="E81" s="25" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F81" s="11">
         <v>20</v>
@@ -4472,7 +4496,7 @@
         <v>1500</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I81" s="12" t="s">
         <v>15</v>
@@ -4481,17 +4505,17 @@
         <v>236.7225</v>
       </c>
       <c r="K81" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L81" s="9">
         <f t="shared" si="1"/>
         <v>4.2243555217607112</v>
       </c>
       <c r="M81" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N81" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
@@ -4502,13 +4526,13 @@
         <v>5307</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D82" s="7">
         <v>70</v>
       </c>
       <c r="E82" s="25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F82" s="7">
         <v>40</v>
@@ -4517,7 +4541,7 @@
         <v>3000</v>
       </c>
       <c r="H82" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I82" s="8" t="s">
         <v>15</v>
@@ -4531,10 +4555,10 @@
         <v>4.2649743248545642</v>
       </c>
       <c r="M82" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N82" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
@@ -4545,13 +4569,13 @@
         <v>6301</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D83" s="7">
         <v>70</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F83" s="7">
         <v>40</v>
@@ -4560,7 +4584,7 @@
         <v>1500</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I83" s="8" t="s">
         <v>15</v>
@@ -4574,10 +4598,10 @@
         <v>8.5299486497091284</v>
       </c>
       <c r="M83" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N83" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
@@ -4588,13 +4612,13 @@
         <v>6302</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D84" s="7">
         <v>135</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F84" s="7">
         <v>20</v>
@@ -4603,7 +4627,7 @@
         <v>1000</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I84" s="8" t="s">
         <v>15</v>
@@ -4617,10 +4641,10 @@
         <v>6.3365332826410672</v>
       </c>
       <c r="M84" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N84" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
@@ -4631,13 +4655,13 @@
         <v>6303</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D85" s="7">
         <v>270</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F85" s="7">
         <v>10</v>
@@ -4646,7 +4670,7 @@
         <v>500</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I85" s="8" t="s">
         <v>15</v>
@@ -4660,7 +4684,7 @@
         <v>6.296555154674877</v>
       </c>
       <c r="M85" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N85" s="5">
         <v>0</v>
@@ -4674,13 +4698,13 @@
         <v>6304</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D86" s="7">
         <v>70</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F86" s="7">
         <v>40</v>
@@ -4689,7 +4713,7 @@
         <v>1500</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I86" s="8" t="s">
         <v>15</v>
@@ -4703,10 +4727,10 @@
         <v>8.5299486497091284</v>
       </c>
       <c r="M86" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N86" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
@@ -4717,13 +4741,13 @@
         <v>6305</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D87" s="7">
         <v>135</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F87" s="7">
         <v>20</v>
@@ -4732,7 +4756,7 @@
         <v>1000</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I87" s="8" t="s">
         <v>15</v>
@@ -4746,10 +4770,10 @@
         <v>6.3365332826410672</v>
       </c>
       <c r="M87" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N87" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
@@ -4760,13 +4784,13 @@
         <v>7101</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D88" s="7">
         <v>35</v>
       </c>
       <c r="E88" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F88" s="7">
         <v>80</v>
@@ -4775,7 +4799,7 @@
         <v>10000</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I88" s="8" t="s">
         <v>15</v>
@@ -4789,7 +4813,7 @@
         <v>2.8571428571428572</v>
       </c>
       <c r="M88" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N88" s="5">
         <v>0</v>
@@ -4803,13 +4827,13 @@
         <v>7103</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D89" s="7">
         <v>35</v>
       </c>
       <c r="E89" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F89" s="7">
         <v>80</v>
@@ -4818,7 +4842,7 @@
         <v>5000</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I89" s="8" t="s">
         <v>15</v>
@@ -4832,7 +4856,7 @@
         <v>5.7142857142857144</v>
       </c>
       <c r="M89" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N89" s="5">
         <v>0</v>
@@ -4846,13 +4870,13 @@
         <v>7104</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D90" s="11">
         <v>35</v>
       </c>
       <c r="E90" s="22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F90" s="11">
         <v>80</v>
@@ -4861,7 +4885,7 @@
         <v>950</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I90" s="12" t="s">
         <v>17</v>
@@ -4870,14 +4894,14 @@
         <v>870</v>
       </c>
       <c r="K90" s="16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L90" s="9">
         <f t="shared" si="1"/>
         <v>1.1494252873563218</v>
       </c>
       <c r="M90" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N90" s="5">
         <v>0</v>
@@ -4891,13 +4915,13 @@
         <v>7202</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D91" s="7">
         <v>18</v>
       </c>
       <c r="E91" s="21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F91" s="7">
         <v>150</v>
@@ -4915,14 +4939,14 @@
         <v>90.5</v>
       </c>
       <c r="K91" s="18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L91" s="9">
         <f t="shared" si="1"/>
         <v>11.049723756906078</v>
       </c>
       <c r="M91" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N91" s="5">
         <v>0</v>
@@ -4936,13 +4960,13 @@
         <v>5308</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D92" s="11">
         <v>90</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F92" s="11">
         <v>30</v>
@@ -4951,7 +4975,7 @@
         <v>2500</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I92" s="12" t="s">
         <v>15</v>
@@ -4960,17 +4984,17 @@
         <v>228</v>
       </c>
       <c r="K92" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L92" s="9">
         <f>1000/J92</f>
         <v>4.3859649122807021</v>
       </c>
       <c r="M92" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N92" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
@@ -4981,13 +5005,13 @@
         <v>6306</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D93" s="7">
         <v>135</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F93" s="7">
         <v>20</v>
@@ -4996,7 +5020,7 @@
         <v>1500</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I93" s="8" t="s">
         <v>15</v>
@@ -5010,15 +5034,131 @@
         <v>4.1152263374485596</v>
       </c>
       <c r="M93" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N93" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P93"/>
     </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A94" s="19">
+        <v>93</v>
+      </c>
+      <c r="B94" s="26">
+        <v>1209</v>
+      </c>
+      <c r="C94" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="D94" s="31">
+        <v>30</v>
+      </c>
+      <c r="E94" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="F94" s="31">
+        <v>100</v>
+      </c>
+      <c r="G94" s="31">
+        <v>5000</v>
+      </c>
+      <c r="H94" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I94" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="J94" s="13">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="K94" s="31"/>
+      <c r="L94" s="13">
+        <v>6.6533599467731195</v>
+      </c>
+      <c r="M94" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="N94" s="28"/>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A95" s="19">
+        <v>94</v>
+      </c>
+      <c r="B95" s="26">
+        <v>1212</v>
+      </c>
+      <c r="C95" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="D95" s="31">
+        <v>30</v>
+      </c>
+      <c r="E95" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="F95" s="31">
+        <v>100</v>
+      </c>
+      <c r="G95" s="31"/>
+      <c r="H95" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I95" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="J95" s="13">
+        <v>179.3</v>
+      </c>
+      <c r="K95" s="31"/>
+      <c r="L95" s="13">
+        <v>5.5772448410485218</v>
+      </c>
+      <c r="M95" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="N95" s="27"/>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A96" s="19">
+        <v>95</v>
+      </c>
+      <c r="B96" s="26">
+        <v>1213</v>
+      </c>
+      <c r="C96" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="D96" s="31">
+        <v>30</v>
+      </c>
+      <c r="E96" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="F96" s="31">
+        <v>100</v>
+      </c>
+      <c r="G96" s="31"/>
+      <c r="H96" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I96" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="13">
+        <v>82.6</v>
+      </c>
+      <c r="K96" s="31"/>
+      <c r="L96" s="13">
+        <v>12.106537530266344</v>
+      </c>
+      <c r="M96" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="N96" s="27"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L91"/>
+  <autoFilter ref="A1:L96"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
